--- a/sheets/조재수대금교본/검수/미운 사랑.xlsx
+++ b/sheets/조재수대금교본/검수/미운 사랑.xlsx
@@ -3121,7 +3121,7 @@
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南∽</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="C3" s="22"/>
@@ -3132,11 +3132,7 @@
         </is>
       </c>
       <c r="E3" s="22"/>
-      <c r="F3" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="F3" s="21"/>
       <c r="G3" s="22"/>
       <c r="H3" s="21" t="inlineStr">
         <is>
@@ -3158,7 +3154,7 @@
       <c r="M3" s="22"/>
       <c r="N3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林∽</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="O3" s="22"/>
@@ -3176,8 +3172,7 @@
       <c r="C4" s="23"/>
       <c r="D4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z
-㴌</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="E4" s="23"/>
@@ -3187,7 +3182,7 @@
       <c r="I4" s="23"/>
       <c r="J4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">∧南林
+          <t xml:space="preserve">南林
 南潢</t>
         </is>
       </c>
@@ -3215,8 +3210,7 @@
       <c r="C5" s="24"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-⌝</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="E5" s="24"/>
@@ -3231,14 +3225,13 @@
       <c r="I5" s="24"/>
       <c r="J5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南∽</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="K5" s="24"/>
       <c r="L5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-И</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="M5" s="24"/>
@@ -3259,7 +3252,7 @@
       <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-林ㄴ</t>
+林</t>
         </is>
       </c>
       <c r="E6" s="22"/>
@@ -3267,8 +3260,7 @@
       <c r="G6" s="22"/>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-И</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="I6" s="22"/>
@@ -3320,7 +3312,7 @@
       <c r="G7" s="23"/>
       <c r="H7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南∽</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I7" s="23"/>
@@ -3345,7 +3337,7 @@
       <c r="O7" s="23"/>
       <c r="P7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南∽</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="Q7" s="23"/>
@@ -3354,8 +3346,7 @@
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z
-㴌</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="C8" s="24"/>
@@ -3372,8 +3363,7 @@
       <c r="I8" s="24"/>
       <c r="J8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z
-㴌</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="K8" s="24"/>
@@ -3388,8 +3378,7 @@
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-⌝</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="C9" s="22"/>
@@ -3428,8 +3417,7 @@
       <c r="B10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-林南
-‹</t>
+林南</t>
         </is>
       </c>
       <c r="C10" s="23"/>
@@ -3438,8 +3426,7 @@
       <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌汰
-潢
-‹</t>
+潢</t>
         </is>
       </c>
       <c r="G10" s="23"/>
@@ -3462,8 +3449,7 @@
       <c r="N10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-林
-‹</t>
+林</t>
         </is>
       </c>
       <c r="O10" s="23"/>
@@ -3475,7 +3461,7 @@
       <c r="B11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢汰
-潢∽</t>
+潢</t>
         </is>
       </c>
       <c r="C11" s="24"/>
@@ -3492,15 +3478,11 @@
         </is>
       </c>
       <c r="G11" s="24"/>
-      <c r="H11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="H11" s="21"/>
       <c r="I11" s="24"/>
       <c r="J11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林∽</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="K11" s="24"/>
@@ -3514,7 +3496,7 @@
       <c r="N11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-南Z</t>
+南</t>
         </is>
       </c>
       <c r="O11" s="24"/>
@@ -3540,7 +3522,7 @@
       <c r="F12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-潢應∽</t>
+潢應</t>
         </is>
       </c>
       <c r="G12" s="22"/>
@@ -3562,7 +3544,7 @@
       <c r="M12" s="22"/>
       <c r="N12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南⌝
+          <t xml:space="preserve">南
 南潢</t>
         </is>
       </c>
@@ -3595,16 +3577,11 @@
       <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-潢
-‹</t>
+潢</t>
         </is>
       </c>
       <c r="I13" s="23"/>
-      <c r="J13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J13" s="21"/>
       <c r="K13" s="23"/>
       <c r="L13" s="21" t="inlineStr">
         <is>
@@ -3614,8 +3591,7 @@
       <c r="M13" s="23"/>
       <c r="N13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-‹</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="O13" s="23"/>

--- a/sheets/조재수대금교본/검수/미운 사랑.xlsx
+++ b/sheets/조재수대금교본/검수/미운 사랑.xlsx
@@ -3121,7 +3121,7 @@
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南∽</t>
         </is>
       </c>
       <c r="C3" s="22"/>
@@ -3132,7 +3132,11 @@
         </is>
       </c>
       <c r="E3" s="22"/>
-      <c r="F3" s="21"/>
+      <c r="F3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="G3" s="22"/>
       <c r="H3" s="21" t="inlineStr">
         <is>
@@ -3154,7 +3158,7 @@
       <c r="M3" s="22"/>
       <c r="N3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林</t>
+          <t xml:space="preserve">林∽</t>
         </is>
       </c>
       <c r="O3" s="22"/>
@@ -3172,7 +3176,8 @@
       <c r="C4" s="23"/>
       <c r="D4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌</t>
+          <t xml:space="preserve">Z
+㴌</t>
         </is>
       </c>
       <c r="E4" s="23"/>
@@ -3182,7 +3187,7 @@
       <c r="I4" s="23"/>
       <c r="J4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南林
+          <t xml:space="preserve">∧南林
 南潢</t>
         </is>
       </c>
@@ -3210,7 +3215,8 @@
       <c r="C5" s="24"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰
+⌝</t>
         </is>
       </c>
       <c r="E5" s="24"/>
@@ -3225,13 +3231,14 @@
       <c r="I5" s="24"/>
       <c r="J5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南∽</t>
         </is>
       </c>
       <c r="K5" s="24"/>
       <c r="L5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林</t>
+          <t xml:space="preserve">林
+И</t>
         </is>
       </c>
       <c r="M5" s="24"/>
@@ -3252,7 +3259,7 @@
       <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-林</t>
+林ㄴ</t>
         </is>
       </c>
       <c r="E6" s="22"/>
@@ -3260,7 +3267,8 @@
       <c r="G6" s="22"/>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢
+И</t>
         </is>
       </c>
       <c r="I6" s="22"/>
@@ -3312,7 +3320,7 @@
       <c r="G7" s="23"/>
       <c r="H7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南∽</t>
         </is>
       </c>
       <c r="I7" s="23"/>
@@ -3337,7 +3345,7 @@
       <c r="O7" s="23"/>
       <c r="P7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南∽</t>
         </is>
       </c>
       <c r="Q7" s="23"/>
@@ -3346,7 +3354,8 @@
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌</t>
+          <t xml:space="preserve">Z
+㴌</t>
         </is>
       </c>
       <c r="C8" s="24"/>
@@ -3363,7 +3372,8 @@
       <c r="I8" s="24"/>
       <c r="J8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌</t>
+          <t xml:space="preserve">Z
+㴌</t>
         </is>
       </c>
       <c r="K8" s="24"/>
@@ -3378,7 +3388,8 @@
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰
+⌝</t>
         </is>
       </c>
       <c r="C9" s="22"/>
@@ -3461,7 +3472,7 @@
       <c r="B11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢汰
-潢</t>
+潢∽</t>
         </is>
       </c>
       <c r="C11" s="24"/>
@@ -3478,11 +3489,15 @@
         </is>
       </c>
       <c r="G11" s="24"/>
-      <c r="H11" s="21"/>
+      <c r="H11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="I11" s="24"/>
       <c r="J11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林</t>
+          <t xml:space="preserve">林∽</t>
         </is>
       </c>
       <c r="K11" s="24"/>
@@ -3496,7 +3511,7 @@
       <c r="N11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-南</t>
+南Z</t>
         </is>
       </c>
       <c r="O11" s="24"/>
@@ -3522,7 +3537,7 @@
       <c r="F12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-潢應</t>
+潢應∽</t>
         </is>
       </c>
       <c r="G12" s="22"/>
@@ -3544,7 +3559,7 @@
       <c r="M12" s="22"/>
       <c r="N12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
+          <t xml:space="preserve">南⌝
 南潢</t>
         </is>
       </c>

--- a/sheets/조재수대금교본/검수/미운 사랑.xlsx
+++ b/sheets/조재수대금교본/검수/미운 사랑.xlsx
@@ -3073,28 +3073,28 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="13.46" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="13.46" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="13.46" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="13.46" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="13.46" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="13.46" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="13.46" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="13.46" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60.61" customHeight="true">
+    <row r="2" ht="74.07" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="90.2" customHeight="true">
+    <row r="3" ht="110.36" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
       </c>
       <c r="Q3" s="22"/>
     </row>
-    <row r="4" ht="90.2" customHeight="true">
+    <row r="4" ht="110.36" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21"/>
       <c r="C4" s="23"/>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="Q4" s="23"/>
     </row>
-    <row r="5" ht="90.2" customHeight="true">
+    <row r="5" ht="110.36" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21"/>
       <c r="C5" s="24"/>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="Q5" s="24"/>
     </row>
-    <row r="6" ht="90.2" customHeight="true">
+    <row r="6" ht="110.36" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21"/>
       <c r="C6" s="22"/>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="Q6" s="22"/>
     </row>
-    <row r="7" ht="90.2" customHeight="true">
+    <row r="7" ht="110.36" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="Q7" s="23"/>
     </row>
-    <row r="8" ht="90.2" customHeight="true">
+    <row r="8" ht="110.36" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
       <c r="P8" s="21"/>
       <c r="Q8" s="24"/>
     </row>
-    <row r="9" ht="90.2" customHeight="true">
+    <row r="9" ht="110.36" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
       <c r="P9" s="21"/>
       <c r="Q9" s="22"/>
     </row>
-    <row r="10" ht="90.2" customHeight="true">
+    <row r="10" ht="110.36" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
       <c r="P10" s="21"/>
       <c r="Q10" s="23"/>
     </row>
-    <row r="11" ht="90.2" customHeight="true">
+    <row r="11" ht="110.36" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="Q11" s="24"/>
     </row>
-    <row r="12" ht="90.2" customHeight="true">
+    <row r="12" ht="110.36" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="22"/>
@@ -3572,7 +3572,7 @@
       </c>
       <c r="Q12" s="22"/>
     </row>
-    <row r="13" ht="90.2" customHeight="true">
+    <row r="13" ht="110.36" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -3618,7 +3618,7 @@
       </c>
       <c r="Q13" s="23"/>
     </row>
-    <row r="14" ht="90.2" customHeight="true">
+    <row r="14" ht="110.36" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -3678,6 +3678,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="66"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="54"/>
 </worksheet>
 </file>